--- a/artfynd/A 48263-2021 artfynd.xlsx
+++ b/artfynd/A 48263-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48263-2021 artfynd.xlsx
+++ b/artfynd/A 48263-2021 artfynd.xlsx
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96646039</v>
+        <v>96646050</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norr om Ristivaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>850703.4776996844</v>
+        <v>850503</v>
       </c>
       <c r="R2" t="n">
-        <v>7519532.763794144</v>
+        <v>7519361</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,33 +746,34 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rätt substrat och alla attribut på fruktkroppen finns men det är en gammal fruktkropp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Tallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96646082</v>
+        <v>96646075</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>851162.5194716115</v>
+        <v>851090</v>
       </c>
       <c r="R3" t="n">
-        <v>7519077.939692308</v>
+        <v>7519104</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +859,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +880,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>högstubbe silverfura</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96646079</v>
+        <v>96646080</v>
       </c>
       <c r="B4" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>851154.8009643191</v>
+        <v>851167</v>
       </c>
       <c r="R4" t="n">
-        <v>7519106.627546332</v>
+        <v>7519082</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,21 +966,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1018,7 +987,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>högstubbe silverfura</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96646076</v>
+        <v>96646041</v>
       </c>
       <c r="B5" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,34 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>1102</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norr om Ristivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>851119.0022134495</v>
+        <v>850619</v>
       </c>
       <c r="R5" t="n">
-        <v>7519094.097390422</v>
+        <v>7519487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,27 +1076,23 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>mycket trolig men Olli Manninen ansåg att den skulle rapporteras som cf.</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1140,7 +1103,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>högstubbe silverfura</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,37 +1121,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96646066</v>
+        <v>96646044</v>
       </c>
       <c r="B6" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>850951.8869591008</v>
+        <v>850534</v>
       </c>
       <c r="R6" t="n">
-        <v>7519204.830240288</v>
+        <v>7519371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,19 +1189,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,37 +1228,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96646075</v>
+        <v>96646078</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>851089.8908220222</v>
+        <v>851155</v>
       </c>
       <c r="R7" t="n">
-        <v>7519103.697921222</v>
+        <v>7519107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,19 +1296,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96646048</v>
+        <v>96646051</v>
       </c>
       <c r="B8" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,21 +1346,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1442,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>850502.8159268454</v>
+        <v>850503</v>
       </c>
       <c r="R8" t="n">
-        <v>7519361.105840959</v>
+        <v>7519361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,19 +1403,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,37 +1442,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96646084</v>
+        <v>96646052</v>
       </c>
       <c r="B9" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1564,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>851196.5098046402</v>
+        <v>850479</v>
       </c>
       <c r="R9" t="n">
-        <v>7519075.171924979</v>
+        <v>7519358</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,21 +1510,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1628,7 +1531,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1646,15 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96646074</v>
+        <v>96646068</v>
       </c>
       <c r="B10" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>851066.6440514247</v>
+        <v>850959</v>
       </c>
       <c r="R10" t="n">
-        <v>7519121.420969225</v>
+        <v>7519159</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,19 +1617,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,37 +1656,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96646071</v>
+        <v>96646074</v>
       </c>
       <c r="B11" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1808,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>850963.8663641806</v>
+        <v>851067</v>
       </c>
       <c r="R11" t="n">
-        <v>7519130.007261436</v>
+        <v>7519121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,21 +1724,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1872,7 +1745,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>hård död silverved</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1890,15 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96646054</v>
+        <v>96646047</v>
       </c>
       <c r="B12" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1930,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>850451.7452622091</v>
+        <v>850526</v>
       </c>
       <c r="R12" t="n">
-        <v>7519292.500760401</v>
+        <v>7519373</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1963,21 +1831,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1990,6 +1848,11 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Tallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2007,15 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96646069</v>
+        <v>96646066</v>
       </c>
       <c r="B13" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2047,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>850967.5276504569</v>
+        <v>850952</v>
       </c>
       <c r="R13" t="n">
-        <v>7519140.149489844</v>
+        <v>7519205</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,21 +1938,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2111,7 +1959,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>högstubbe silverfura</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2129,15 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96646080</v>
+        <v>96646079</v>
       </c>
       <c r="B14" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2169,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>851167.4258198097</v>
+        <v>851155</v>
       </c>
       <c r="R14" t="n">
-        <v>7519081.68720613</v>
+        <v>7519107</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,21 +2045,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2233,7 +2066,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>högstubbe silverfura</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2251,15 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96646042</v>
+        <v>96646071</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2291,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>850604.6133819736</v>
+        <v>850964</v>
       </c>
       <c r="R15" t="n">
-        <v>7519434.586289515</v>
+        <v>7519130</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2324,21 +2152,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2355,7 +2173,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>högstubbe silverfura</t>
+          <t>hård död silverved</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2373,15 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96646035</v>
+        <v>96646039</v>
       </c>
       <c r="B16" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2413,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>850763.1207159149</v>
+        <v>850703</v>
       </c>
       <c r="R16" t="n">
-        <v>7519390.627543717</v>
+        <v>7519533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,21 +2259,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2473,11 +2276,6 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>Tallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2495,37 +2293,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96646064</v>
+        <v>96646054</v>
       </c>
       <c r="B17" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5260</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2535,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>850808.1791921278</v>
+        <v>850452</v>
       </c>
       <c r="R17" t="n">
-        <v>7519334.146370255</v>
+        <v>7519293</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,31 +2361,16 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>mycket ungt exemplar men bruna kanter på fruktkroppen</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2600,11 +2378,6 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Tallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2622,37 +2395,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96646060</v>
+        <v>96646048</v>
       </c>
       <c r="B18" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2662,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>850634.9382846567</v>
+        <v>850503</v>
       </c>
       <c r="R18" t="n">
-        <v>7519271.912465752</v>
+        <v>7519361</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2695,21 +2463,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2726,7 +2484,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2744,53 +2502,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96646041</v>
+        <v>96646064</v>
       </c>
       <c r="B19" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1102</v>
+        <v>5260</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norr om Ristivaara, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>850619.1512904509</v>
+        <v>850808</v>
       </c>
       <c r="R19" t="n">
-        <v>7519487.483807955</v>
+        <v>7519334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2820,24 +2570,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>mycket trolig men Olli Manninen ansåg att den skulle rapporteras som cf.</t>
+          <t>mycket ungt exemplar men bruna kanter på fruktkroppen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,7 +2586,6 @@
       <c r="AE19" t="b">
         <v>1</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2875,37 +2614,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96646072</v>
+        <v>96646083</v>
       </c>
       <c r="B20" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5260</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2915,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>850961.9732237339</v>
+        <v>851196</v>
       </c>
       <c r="R20" t="n">
-        <v>7519123.962684615</v>
+        <v>7519073</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,26 +2682,21 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>mycket ungt exemplar men med bruna kanter på fruktkroppen</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2997,37 +2726,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96646067</v>
+        <v>96646072</v>
       </c>
       <c r="B21" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3037,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>850963.1393244446</v>
+        <v>850962</v>
       </c>
       <c r="R21" t="n">
-        <v>7519184.338435907</v>
+        <v>7519124</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,21 +2794,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3101,7 +2815,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>högstubbe silverfura</t>
+          <t>silverlåga av tall</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3119,15 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96646062</v>
+        <v>96646042</v>
       </c>
       <c r="B22" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>850754.294688335</v>
+        <v>850605</v>
       </c>
       <c r="R22" t="n">
-        <v>7519315.334091782</v>
+        <v>7519435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3192,21 +2901,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +2922,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>högstubbe silverfura</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3241,15 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96646078</v>
+        <v>96646053</v>
       </c>
       <c r="B23" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,21 +2951,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3281,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>851154.8009643191</v>
+        <v>850430</v>
       </c>
       <c r="R23" t="n">
-        <v>7519106.627546332</v>
+        <v>7519314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3314,21 +3008,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3345,7 +3029,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3363,15 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96646037</v>
+        <v>96646060</v>
       </c>
       <c r="B24" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3379,21 +3058,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3403,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>850708.8860602075</v>
+        <v>850635</v>
       </c>
       <c r="R24" t="n">
-        <v>7519506.858552685</v>
+        <v>7519272</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3436,19 +3115,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3485,37 +3154,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96646051</v>
+        <v>96646062</v>
       </c>
       <c r="B25" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3525,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>850502.8159268454</v>
+        <v>850754</v>
       </c>
       <c r="R25" t="n">
-        <v>7519361.105840959</v>
+        <v>7519315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3558,21 +3222,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3589,7 +3243,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3607,15 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96646044</v>
+        <v>96646073</v>
       </c>
       <c r="B26" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3623,21 +3272,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3647,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>850533.6043290596</v>
+        <v>851003</v>
       </c>
       <c r="R26" t="n">
-        <v>7519370.638986296</v>
+        <v>7519134</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3680,21 +3329,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3711,7 +3350,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3729,15 +3368,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96646057</v>
+        <v>96646059</v>
       </c>
       <c r="B27" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3745,21 +3379,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3769,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>850494.6435094443</v>
+        <v>850635</v>
       </c>
       <c r="R27" t="n">
-        <v>7519280.884473323</v>
+        <v>7519272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3802,19 +3436,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3851,15 +3475,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96646059</v>
+        <v>96646067</v>
       </c>
       <c r="B28" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3891,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>850634.9382846567</v>
+        <v>850963</v>
       </c>
       <c r="R28" t="n">
-        <v>7519271.912465752</v>
+        <v>7519184</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3924,21 +3543,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3955,7 +3564,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>högstubbe silverfura</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3973,15 +3582,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96646047</v>
+        <v>96646076</v>
       </c>
       <c r="B29" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3989,21 +3593,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4013,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>850525.5053392993</v>
+        <v>851119</v>
       </c>
       <c r="R29" t="n">
-        <v>7519373.412370591</v>
+        <v>7519094</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4046,21 +3650,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4077,7 +3671,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>högstubbe silverfura</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4095,15 +3689,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96646063</v>
+        <v>96646035</v>
       </c>
       <c r="B30" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>850754.294688335</v>
+        <v>850763</v>
       </c>
       <c r="R30" t="n">
-        <v>7519315.334091782</v>
+        <v>7519391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4168,19 +3757,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4217,37 +3796,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96646083</v>
+        <v>96646037</v>
       </c>
       <c r="B31" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5260</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4257,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>851196.3849962131</v>
+        <v>850709</v>
       </c>
       <c r="R31" t="n">
-        <v>7519073.224947464</v>
+        <v>7519507</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4290,31 +3864,16 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>mycket ungt exemplar men med bruna kanter på fruktkroppen</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -4326,7 +3885,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4344,15 +3903,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96646077</v>
+        <v>96646055</v>
       </c>
       <c r="B32" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4384,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>851125.8753090731</v>
+        <v>850490</v>
       </c>
       <c r="R32" t="n">
-        <v>7519106.215736494</v>
+        <v>7519269</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4417,19 +3971,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4466,37 +4010,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96646052</v>
+        <v>96646057</v>
       </c>
       <c r="B33" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4506,10 +4045,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>850478.9059616968</v>
+        <v>850495</v>
       </c>
       <c r="R33" t="n">
-        <v>7519357.899138123</v>
+        <v>7519281</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4539,21 +4078,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4570,7 +4099,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4588,15 +4117,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96646055</v>
+        <v>96646061</v>
       </c>
       <c r="B34" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4628,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>850490.0455944334</v>
+        <v>850635</v>
       </c>
       <c r="R34" t="n">
-        <v>7519269.074323399</v>
+        <v>7519272</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4661,19 +4185,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4710,15 +4224,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96646073</v>
+        <v>96646063</v>
       </c>
       <c r="B35" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4726,21 +4235,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4750,10 +4259,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>851002.7849593193</v>
+        <v>850754</v>
       </c>
       <c r="R35" t="n">
-        <v>7519133.689548089</v>
+        <v>7519315</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4783,21 +4292,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4814,7 +4313,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>dimensionsavverkningsstubbe</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4832,15 +4331,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96646061</v>
+        <v>96646077</v>
       </c>
       <c r="B36" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4872,10 +4366,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>850634.9382846567</v>
+        <v>851126</v>
       </c>
       <c r="R36" t="n">
-        <v>7519271.912465752</v>
+        <v>7519106</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4905,19 +4399,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4954,15 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96646053</v>
+        <v>96646084</v>
       </c>
       <c r="B37" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4970,21 +4449,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4994,10 +4473,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>850430.2738251409</v>
+        <v>851197</v>
       </c>
       <c r="R37" t="n">
-        <v>7519314.324123624</v>
+        <v>7519075</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5027,21 +4506,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5058,7 +4527,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>dimensionsavverkningsstubbe</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5076,37 +4545,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96646068</v>
+        <v>96646069</v>
       </c>
       <c r="B38" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5116,10 +4580,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>850959.1865787006</v>
+        <v>850968</v>
       </c>
       <c r="R38" t="n">
-        <v>7519159.102510204</v>
+        <v>7519140</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5149,21 +4613,11 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5180,7 +4634,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>högstubbe silverfura</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5198,53 +4652,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96646050</v>
+        <v>96646082</v>
       </c>
       <c r="B39" t="n">
-        <v>89659</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>71</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norr om Ristivaara, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>850502.8159268454</v>
+        <v>851163</v>
       </c>
       <c r="R39" t="n">
-        <v>7519361.105840959</v>
+        <v>7519078</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5274,33 +4720,17 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rätt substrat och alla attribut på fruktkroppen finns men det är en gammal fruktkropp.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5311,7 +4741,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>silverlåga av tall</t>
+          <t>högstubbe silverfura</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>

--- a/artfynd/A 48263-2021 artfynd.xlsx
+++ b/artfynd/A 48263-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646050</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646041</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646044</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646078</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646052</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646068</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646074</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646047</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1974,6 +2034,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646066</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646079</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646071</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2290,6 +2365,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646039</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,6 +2472,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646054</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2499,6 +2584,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646048</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2611,6 +2701,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646064</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2723,6 +2818,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646083</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2830,6 +2930,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646072</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2937,6 +3042,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646042</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3044,6 +3154,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646053</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3151,6 +3266,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646060</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3258,6 +3378,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646062</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3365,6 +3490,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646073</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3472,6 +3602,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646059</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3579,6 +3714,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646067</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3686,6 +3826,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646076</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3793,6 +3938,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646035</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3900,6 +4050,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646037</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4007,6 +4162,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646055</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4114,6 +4274,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646057</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4221,6 +4386,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646061</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4328,6 +4498,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646063</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4435,6 +4610,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646077</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4542,6 +4722,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646084</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4649,6 +4834,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646069</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4756,8 +4946,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96646082</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>